--- a/docs/gift-finder-tags.xlsx
+++ b/docs/gift-finder-tags.xlsx
@@ -2,33 +2,43 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-3060" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="라인별 추천태그" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="읽어주세요" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -40,7 +50,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="008A6D3B"/>
+        <fgColor rgb="FF8A6D3B"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,7 +76,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -430,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -443,7 +453,7 @@
     <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="21.95" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>라인ID</t>
@@ -490,7 +500,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="49.5" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>rose-hydrangea-bouquet</t>
@@ -513,7 +523,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>기념일, 프러포즈, 생일, 화이트데이, 발렌타인데이, 크리스마스, 병문안</t>
+          <t>기념일, 프러포즈, 생일, 화이트데이, 발렌타인데이, 크리스마스, 병문안, 승진·퇴임, 졸업·입학</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -531,9 +541,9 @@
           <t>장미와 수국을 함께 엮은 프리저브드 꽃다발이라 생화처럼 며칠 만에 시들지 않고, 받은 날 그대로의 모습이 오래 남아요.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
+      <c r="I2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="49.5" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>hydrangea-bouquet</t>
@@ -574,9 +584,9 @@
           <t>수국은 색이 은은해서 취향을 크게 타지 않고, 프리저브드라 오래 두고 볼 수 있어요. 순수 프리저브드 소재라 물 관리가 필요 없어 병문안에도 부담 없어요.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="I3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="33" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>superior-rose</t>
@@ -599,7 +609,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>프러포즈, 기념일, 화이트데이, 발렌타인데이, 병문안</t>
+          <t>프러포즈, 기념일, 화이트데이, 발렌타인데이, 병문안, 승진·퇴임, 졸업·입학</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -617,9 +627,9 @@
           <t>큰 송이 프리저브드 장미 한 종으로 구성해 꽃 자체가 주인공이 되는 구성이에요.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="I4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="33" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>rose-soap-bouquet</t>
@@ -642,7 +652,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>생일, 기념일, 화이트데이, 발렌타인데이</t>
+          <t>생일, 기념일, 화이트데이, 발렌타인데이, 졸업·입학</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -660,9 +670,9 @@
           <t>비누로 만든 꽃송이라 은은한 향이 함께 나요. 향이 부담스러우면 무향 옵션도 있습니다.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="I5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="33" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>pinkpeach-bouquet</t>
@@ -703,9 +713,9 @@
           <t>핑크와 피치 톤을 섞어 사진에 특히 예쁘게 담기는 조합이에요.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="I6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="33" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>sunflower-bouquet</t>
@@ -746,9 +756,9 @@
           <t>해바라기는 예로부터 재물운을 상징해 개업·집들이 선물로 많이 찾으세요.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="I7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="33" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>carnation-rose-bouquet</t>
@@ -771,7 +781,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>어버이날, 스승의날, 생신·환갑</t>
+          <t>생신·환갑, 어버이날, 설날·명절, 칠순, 팔순</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -789,9 +799,9 @@
           <t>카네이션과 장미를 함께 엮어 카네이션만 있을 때보다 풍성하고, 시들지 않아 오래 두고 보실 수 있어요.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="I8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="33" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>carnation-money-bouquet</t>
@@ -814,7 +824,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>어버이날, 생신·환갑, 칠순·팔순</t>
+          <t>생신·환갑, 어버이날, 설날·명절, 칠순, 팔순</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -832,9 +842,9 @@
           <t>카네이션 사이에 지폐를 꽂는 구조라 현금의 실용성과 꽃의 정성을 같이 전할 수 있어요.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="I9" s="2" t="n"/>
+    </row>
+    <row r="10" ht="33" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>rose-money-bouquet</t>
@@ -857,7 +867,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>생신·환갑, 칠순·팔순, 어버이날</t>
+          <t>생신·환갑, 어버이날, 설날·명절, 칠순, 팔순</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -875,9 +885,9 @@
           <t>며느리·사위·손주가 어른께 드리는 선물로 가장 많이 찾는 구성이에요.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="I10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="33" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>single-stem-soap-box</t>
@@ -918,9 +928,9 @@
           <t>1만원 안쪽 가격에 투명 박스까지 포함이라 답례품이나 단체 선물로 쓰기 좋아요.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="I11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="33" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>kinderjoy-doll-bouquet</t>
@@ -943,7 +953,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>발표회·재롱잔치, 졸업·입학, 생일</t>
+          <t>생일, 발표회·재롱잔치, 학예회, 유치원·초등학교 졸업·입학</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -961,9 +971,9 @@
           <t>꽃과 인형에 킨더조이까지 들어 있어 아이가 바로 좋아하고, 사진에서 아이 얼굴을 가리지 않는 크기예요.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="I12" s="2" t="n"/>
+    </row>
+    <row r="13" ht="33" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>character-doll-bouquet</t>
@@ -986,7 +996,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>생일, 발표회·재롱잔치, 졸업·입학</t>
+          <t>생일, 발표회·재롱잔치, 학예회, 유치원·초등학교 졸업·입학</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1004,9 +1014,9 @@
           <t>마이멜로디·시나모롤 인형이 함께 있어 꽃다발을 받은 뒤에도 인형은 계속 곁에 둘 수 있어요.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
+      <c r="I13" s="2" t="n"/>
+    </row>
+    <row r="14" ht="33" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>rebony-trophy-doll-bouquet</t>
@@ -1029,7 +1039,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>발표회·재롱잔치, 졸업·입학</t>
+          <t>생일, 발표회·재롱잔치, 학예회, 유치원·초등학교 졸업·입학</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1047,9 +1057,9 @@
           <t>트로피 모양 포트에 담겨 있어 시상식 분위기가 나고, 행사 뒤엔 방에 두는 소품이 돼요.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
+      <c r="I14" s="2" t="n"/>
+    </row>
+    <row r="15" ht="49.5" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>glassdome-moodlamp</t>
@@ -1090,9 +1100,9 @@
           <t>유리돔 안에 꽃을 담고 조명을 넣어, 꽃 선물이면서 동시에 인테리어 조명 역할을 해요. 물이 없어 병실에 가져가도 관리 부담이 없어요.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
+      <c r="I15" s="2" t="n"/>
+    </row>
+    <row r="16" ht="33" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>classic-money-box</t>
@@ -1115,7 +1125,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>생신·환갑, 어버이날, 설날·명절</t>
+          <t>생신·환갑, 어버이날, 설날·명절, 칠순, 팔순</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1133,9 +1143,9 @@
           <t>투명 박스라 안에 든 꽃과 현금이 함께 보이고, 돈티슈·머니캡 두 방식 중 고를 수 있어요.</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
+      <c r="I16" s="2" t="n"/>
+    </row>
+    <row r="17" ht="33" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>premium-window-money-box</t>
@@ -1158,7 +1168,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>생신·환갑, 어버이날, 설날·명절</t>
+          <t>생신·환갑, 어버이날, 설날·명절, 칠순, 팔순</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1176,9 +1186,9 @@
           <t>창문형 박스에 꽃을 배치해 정면에서 봤을 때 정돈된 느낌이 나요. 스몰·라지 두 크기가 있습니다.</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
+      <c r="I17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="33" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>sunflower-frame</t>
@@ -1201,7 +1211,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>집들이·개업, 승진·퇴임</t>
+          <t>집들이·개업, 승진·퇴임, 실내 인테리어</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1219,9 +1229,9 @@
           <t>재물운을 상징하는 해바라기를 액자에 담아, 매장이나 거실에 걸어두기 좋아요.</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr"/>
-    </row>
-    <row r="19">
+      <c r="I18" s="2" t="n"/>
+    </row>
+    <row r="19" ht="49.5" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>cup-moodlamp-single</t>
@@ -1262,9 +1272,9 @@
           <t>컵 모양 무드등에 꽃 한 송이를 담은 구성이라 책상이나 머리맡에 두기 좋은 크기예요. 물을 안 갈아줘도 돼서 병실에도 부담 없어요.</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr"/>
-    </row>
-    <row r="20">
+      <c r="I19" s="2" t="n"/>
+    </row>
+    <row r="20" ht="33" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>ionantha-moodlamp</t>
@@ -1287,7 +1297,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>집들이·개업, 승진·퇴임</t>
+          <t>집들이·개업, 승진·퇴임, 취미·자기계발</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1305,9 +1315,9 @@
           <t>이오난사와 스칸디아모스는 물 주기가 거의 필요 없는 공기정화 식물이라, 관리할 시간이 없어도 괜찮아요.</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="I20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="33" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>centerpiece</t>
@@ -1348,9 +1358,9 @@
           <t>사방 어느 각도에서 봐도 균형이 잡히도록 만든 구성이라 테이블 가운데 두기에 맞아요.</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
+      <c r="I21" s="2" t="n"/>
+    </row>
+    <row r="22" ht="33" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>topiary-moodlamp</t>
@@ -1373,7 +1383,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>집들이·개업, 생일, 기념일, 크리스마스</t>
+          <t>집들이·개업, 생일, 기념일, 크리스마스, 프러포즈</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1391,9 +1401,9 @@
           <t>동그랗게 다듬은 수국에 LED를 넣어, 불을 켜면 화분이 조명이 되는 구조예요.</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr"/>
-    </row>
-    <row r="23">
+      <c r="I22" s="2" t="n"/>
+    </row>
+    <row r="23" ht="33" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>money-cake</t>
@@ -1416,7 +1426,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>생신·환갑, 칠순·팔순, 어버이날</t>
+          <t>생신·환갑, 어버이날, 설날·명절, 칠순, 팔순</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1434,9 +1444,9 @@
           <t>케이크 모양에 현금을 꽂고 LED 조명까지 들어가, 촛불 대신 불을 켜고 축하하는 자리를 만들 수 있어요.</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
+      <c r="I23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="49.5" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>hydrangea-moodlamp</t>
@@ -1477,9 +1487,9 @@
           <t>프리저브드 수국을 가득 채우고 조명을 넣은 대표 상품이에요. 전원은 USB와 건전지 중 고를 수 있고, USB 쪽 선호가 조금 더 많습니다.</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
+      <c r="I24" s="2" t="n"/>
+    </row>
+    <row r="25" ht="49.5" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>flower-postcard</t>
@@ -1520,9 +1530,9 @@
           <t>크래프트 카드에 미니 드라이플라워를 붙여, 카드 자체가 작은 꽃다발이 돼요.</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
+      <c r="I25" s="2" t="n"/>
+    </row>
+    <row r="26" ht="33" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>flower-class</t>
@@ -1571,6 +1581,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="256" horizontalDpi="203" verticalDpi="203"/>
 </worksheet>
 </file>
 
@@ -1581,7 +1592,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
@@ -1593,9 +1604,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
